--- a/survey_templates/036_wedding_venue_check_out_form--survey_templates.xlsx
+++ b/survey_templates/036_wedding_venue_check_out_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>return_date</t>
+          <t>return_date_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Return Date</t>
+          <t>Return Date 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>return_time</t>
+          <t>return_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Return Time</t>
+          <t>Return Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>return_status</t>
+          <t>return_status_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Return Status</t>
+          <t>Return Status 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>comments_returned</t>
+          <t>comments_returned_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Comments Returned</t>
+          <t>Comments Returned 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>contact_person</t>
+          <t>contact_person_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Contact Person</t>
+          <t>Contact Person 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>comments_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Comments 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'wedding',_'value':_'wedding'}</t>
+          <t>wedding</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Wedding', 'value': 'Wedding'}</t>
+          <t>Wedding</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'birthday',_'value':_'birthday'}</t>
+          <t>birthday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Birthday', 'value': 'Birthday'}</t>
+          <t>Birthday</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'company_party',_'value':_'company_party'}</t>
+          <t>company_party</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Company Party', 'value': 'Company Party'}</t>
+          <t>Company Party</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_checked',_'value':_1}</t>
+          <t>not_checked</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Checked', 'value': 1}</t>
+          <t>Not Checked</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'checked',_'value':_2}</t>
+          <t>checked</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Checked', 'value': 2}</t>
+          <t>Checked</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'chairs',_'value':_1}</t>
+          <t>chairs</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Chairs', 'value': 1}</t>
+          <t>Chairs</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tables',_'value':_2}</t>
+          <t>tables</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tables', 'value': 2}</t>
+          <t>Tables</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'linens',_'value':_3}</t>
+          <t>linens</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Linens', 'value': 3}</t>
+          <t>Linens</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_returned',_'value':_1}</t>
+          <t>not_returned</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Returned', 'value': 1}</t>
+          <t>Not Returned</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1284,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'returned',_'value':_2}</t>
+          <t>returned</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Returned', 'value': 2}</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>return_status_choices</t>
+          <t>return_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'not_returned',_'value':_1}</t>
+          <t>not_returned</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Not Returned', 'value': 1}</t>
+          <t>Not Returned</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>return_status_choices</t>
+          <t>return_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'returned',_'value':_2}</t>
+          <t>returned</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Returned', 'value': 2}</t>
+          <t>Returned</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_1}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 1}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
